--- a/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold/reinforcement_learning/mol2mol_scaffold_rl_generated_optimal.xlsx
+++ b/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold/reinforcement_learning/mol2mol_scaffold_rl_generated_optimal.xlsx
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="AA2" s="3">
-        <v>34.03657531738281</v>
+        <v>34.036575</v>
       </c>
       <c r="AB2" s="3">
-        <v>35.33199691772461</v>
+        <v>35.331997</v>
       </c>
       <c r="AC2" s="3">
-        <v>45.15724182128906</v>
+        <v>45.15724</v>
       </c>
       <c r="AD2" s="3">
         <v>0</v>
@@ -1741,55 +1741,55 @@
         <v>0</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.4128182828426361</v>
+        <v>0.41281828</v>
       </c>
       <c r="AH2" s="3">
-        <v>0.317070335149765</v>
+        <v>0.31707034</v>
       </c>
       <c r="AI2" s="3">
-        <v>0.8789542317390442</v>
+        <v>0.8789542299999999</v>
       </c>
       <c r="AJ2" s="3">
-        <v>0.05042798444628716</v>
+        <v>0.050427984</v>
       </c>
       <c r="AK2" s="3">
-        <v>0.8694758415222168</v>
+        <v>0.86947584</v>
       </c>
       <c r="AL2" s="3">
-        <v>0.4486382901668549</v>
+        <v>0.4486383</v>
       </c>
       <c r="AM2" s="3">
-        <v>0.7849494814872742</v>
+        <v>0.7849495</v>
       </c>
       <c r="AN2" s="3">
-        <v>0.8201218843460083</v>
+        <v>0.8201219</v>
       </c>
       <c r="AO2" s="3">
-        <v>0.2035863697528839</v>
+        <v>0.20358637</v>
       </c>
       <c r="AP2" s="3">
-        <v>0.9765839576721191</v>
+        <v>0.97658396</v>
       </c>
       <c r="AQ2" s="3">
-        <v>0.9999567866325378</v>
+        <v>0.9999568</v>
       </c>
       <c r="AR2" s="3">
-        <v>0.7418512105941772</v>
+        <v>0.7418512</v>
       </c>
       <c r="AS2" s="3">
-        <v>0.9514479637145996</v>
+        <v>0.95144796</v>
       </c>
       <c r="AT2" s="3">
-        <v>0.8597750663757324</v>
+        <v>0.85977507</v>
       </c>
       <c r="AU2" s="3">
-        <v>-4.779772758483887</v>
+        <v>-4.7797728</v>
       </c>
       <c r="AV2" s="3">
-        <v>96.93354797363281</v>
+        <v>96.93355</v>
       </c>
       <c r="AW2" s="3">
-        <v>8.543522834777832</v>
+        <v>8.543523</v>
       </c>
       <c r="AX2" s="3">
         <v>432.5240000000002</v>
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="AA3" s="3">
-        <v>54.03302001953125</v>
+        <v>54.03302</v>
       </c>
       <c r="AB3" s="3">
-        <v>51.58975982666016</v>
+        <v>51.58976</v>
       </c>
       <c r="AC3" s="3">
-        <v>46.11928558349609</v>
+        <v>46.119286</v>
       </c>
       <c r="AD3" s="3">
         <v>0</v>
@@ -1922,55 +1922,55 @@
         <v>0</v>
       </c>
       <c r="AG3" s="3">
-        <v>0.1514938920736313</v>
+        <v>0.15149389</v>
       </c>
       <c r="AH3" s="3">
-        <v>0.3794129192829132</v>
+        <v>0.37941292</v>
       </c>
       <c r="AI3" s="3">
-        <v>0.790505588054657</v>
+        <v>0.7905056</v>
       </c>
       <c r="AJ3" s="3">
-        <v>0.05281468480825424</v>
+        <v>0.052814685</v>
       </c>
       <c r="AK3" s="3">
-        <v>0.8946078419685364</v>
+        <v>0.89460784</v>
       </c>
       <c r="AL3" s="3">
-        <v>0.4100112020969391</v>
+        <v>0.4100112</v>
       </c>
       <c r="AM3" s="3">
-        <v>0.616396963596344</v>
+        <v>0.61639696</v>
       </c>
       <c r="AN3" s="3">
-        <v>0.7340325713157654</v>
+        <v>0.7340326</v>
       </c>
       <c r="AO3" s="3">
-        <v>0.2590197920799255</v>
+        <v>0.2590198</v>
       </c>
       <c r="AP3" s="3">
-        <v>0.9837437868118286</v>
+        <v>0.9837437999999999</v>
       </c>
       <c r="AQ3" s="3">
-        <v>0.9999759793281555</v>
+        <v>0.999976</v>
       </c>
       <c r="AR3" s="3">
-        <v>0.7540546655654907</v>
+        <v>0.75405467</v>
       </c>
       <c r="AS3" s="3">
-        <v>0.9556648135185242</v>
+        <v>0.9556648</v>
       </c>
       <c r="AT3" s="3">
-        <v>0.8375112414360046</v>
+        <v>0.83751124</v>
       </c>
       <c r="AU3" s="3">
-        <v>-4.578262329101562</v>
+        <v>-4.5782623</v>
       </c>
       <c r="AV3" s="3">
-        <v>98.41603851318359</v>
+        <v>98.41604</v>
       </c>
       <c r="AW3" s="3">
-        <v>6.461910247802734</v>
+        <v>6.4619102</v>
       </c>
       <c r="AX3" s="3">
         <v>421.4720000000002</v>
@@ -2041,22 +2041,22 @@
         <v>1.111841230495139</v>
       </c>
       <c r="M4" s="3">
-        <v>0.3282061778321487</v>
+        <v>0.3282061778321486</v>
       </c>
       <c r="N4" s="3">
         <v>16.431809456578</v>
       </c>
       <c r="O4" s="3">
-        <v>9.936063026787181</v>
+        <v>9.936063026787179</v>
       </c>
       <c r="P4" s="3">
         <v>4.888158769504861</v>
       </c>
       <c r="Q4" s="3">
-        <v>0.3282061778321487</v>
+        <v>0.3282061778321486</v>
       </c>
       <c r="R4" s="3">
-        <v>2.941420547870539</v>
+        <v>2.941420547870538</v>
       </c>
       <c r="S4" s="3">
         <v>56.90171276650422</v>
@@ -2068,7 +2068,7 @@
         <v>5.531442878055872</v>
       </c>
       <c r="V4" s="3">
-        <v>0.3282061778321487</v>
+        <v>0.3282061778321486</v>
       </c>
       <c r="W4" s="3">
         <v>3.108700000000002</v>
@@ -2085,13 +2085,13 @@
         </is>
       </c>
       <c r="AA4" s="3">
-        <v>45.32907104492188</v>
+        <v>45.32907</v>
       </c>
       <c r="AB4" s="3">
-        <v>40.65900039672852</v>
+        <v>40.659</v>
       </c>
       <c r="AC4" s="3">
-        <v>48.0501594543457</v>
+        <v>48.05016</v>
       </c>
       <c r="AD4" s="3">
         <v>1</v>
@@ -2103,55 +2103,55 @@
         <v>0</v>
       </c>
       <c r="AG4" s="3">
-        <v>0.102793276309967</v>
+        <v>0.10279328</v>
       </c>
       <c r="AH4" s="3">
-        <v>0.4763052463531494</v>
+        <v>0.47630525</v>
       </c>
       <c r="AI4" s="3">
-        <v>0.8466208577156067</v>
+        <v>0.84662086</v>
       </c>
       <c r="AJ4" s="3">
-        <v>0.07957594841718674</v>
+        <v>0.07957595000000001</v>
       </c>
       <c r="AK4" s="3">
-        <v>0.9252824783325195</v>
+        <v>0.9252825</v>
       </c>
       <c r="AL4" s="3">
-        <v>0.1209559068083763</v>
+        <v>0.12095591</v>
       </c>
       <c r="AM4" s="3">
-        <v>0.5362284779548645</v>
+        <v>0.5362285</v>
       </c>
       <c r="AN4" s="3">
-        <v>0.7878203392028809</v>
+        <v>0.78782034</v>
       </c>
       <c r="AO4" s="3">
-        <v>0.2861897349357605</v>
+        <v>0.28618973</v>
       </c>
       <c r="AP4" s="3">
-        <v>0.9864606857299805</v>
+        <v>0.9864607</v>
       </c>
       <c r="AQ4" s="3">
-        <v>0.9998184442520142</v>
+        <v>0.99981844</v>
       </c>
       <c r="AR4" s="3">
-        <v>0.736710250377655</v>
+        <v>0.73671025</v>
       </c>
       <c r="AS4" s="3">
-        <v>0.8996855020523071</v>
+        <v>0.8996855</v>
       </c>
       <c r="AT4" s="3">
-        <v>0.9100499153137207</v>
+        <v>0.9100499</v>
       </c>
       <c r="AU4" s="3">
-        <v>-5.027266979217529</v>
+        <v>-5.027267</v>
       </c>
       <c r="AV4" s="3">
-        <v>98.09504699707031</v>
+        <v>98.09505</v>
       </c>
       <c r="AW4" s="3">
-        <v>11.3743371963501</v>
+        <v>11.374337</v>
       </c>
       <c r="AX4" s="3">
         <v>476.5770000000003</v>
@@ -2228,7 +2228,7 @@
         <v>19.74910864197922</v>
       </c>
       <c r="O5" s="3">
-        <v>11.37905879034133</v>
+        <v>11.37905879034132</v>
       </c>
       <c r="P5" s="3">
         <v>4.814098593944639</v>
@@ -2266,13 +2266,13 @@
         </is>
       </c>
       <c r="AA5" s="3">
-        <v>43.11553192138672</v>
+        <v>43.115532</v>
       </c>
       <c r="AB5" s="3">
-        <v>43.15958786010742</v>
+        <v>43.159588</v>
       </c>
       <c r="AC5" s="3">
-        <v>47.59580993652344</v>
+        <v>47.59581</v>
       </c>
       <c r="AD5" s="3">
         <v>0</v>
@@ -2284,55 +2284,55 @@
         <v>0</v>
       </c>
       <c r="AG5" s="3">
-        <v>0.3113523125648499</v>
+        <v>0.3113523</v>
       </c>
       <c r="AH5" s="3">
-        <v>0.2100279033184052</v>
+        <v>0.2100279</v>
       </c>
       <c r="AI5" s="3">
-        <v>0.8713839650154114</v>
+        <v>0.87138397</v>
       </c>
       <c r="AJ5" s="3">
-        <v>0.05258895084261894</v>
+        <v>0.05258895</v>
       </c>
       <c r="AK5" s="3">
-        <v>0.7567367553710938</v>
+        <v>0.75673676</v>
       </c>
       <c r="AL5" s="3">
-        <v>0.4072732925415039</v>
+        <v>0.4072733</v>
       </c>
       <c r="AM5" s="3">
-        <v>0.7121190428733826</v>
+        <v>0.71211904</v>
       </c>
       <c r="AN5" s="3">
-        <v>0.7431508898735046</v>
+        <v>0.7431508999999999</v>
       </c>
       <c r="AO5" s="3">
-        <v>0.1270819902420044</v>
+        <v>0.12708199</v>
       </c>
       <c r="AP5" s="3">
-        <v>0.9562612771987915</v>
+        <v>0.9562613</v>
       </c>
       <c r="AQ5" s="3">
-        <v>0.9999759793281555</v>
+        <v>0.999976</v>
       </c>
       <c r="AR5" s="3">
-        <v>0.7629089951515198</v>
+        <v>0.7629089999999999</v>
       </c>
       <c r="AS5" s="3">
-        <v>0.960793673992157</v>
+        <v>0.9607937</v>
       </c>
       <c r="AT5" s="3">
-        <v>0.7639257907867432</v>
+        <v>0.7639258</v>
       </c>
       <c r="AU5" s="3">
-        <v>-4.43918514251709</v>
+        <v>-4.439185</v>
       </c>
       <c r="AV5" s="3">
-        <v>93.70291900634766</v>
+        <v>93.70292000000001</v>
       </c>
       <c r="AW5" s="3">
-        <v>8.161908149719238</v>
+        <v>8.161908</v>
       </c>
       <c r="AX5" s="3">
         <v>439.4620000000002</v>
@@ -2350,7 +2350,7 @@
         <v>5.692319404685037</v>
       </c>
       <c r="BC5" s="3">
-        <v>0.4786311772572182</v>
+        <v>0.4786311772572181</v>
       </c>
       <c r="BD5" s="3">
         <v>1</v>
@@ -2447,13 +2447,13 @@
         </is>
       </c>
       <c r="AA6" s="3">
-        <v>65.06654357910156</v>
+        <v>65.06654</v>
       </c>
       <c r="AB6" s="3">
-        <v>61.67655563354492</v>
+        <v>61.676556</v>
       </c>
       <c r="AC6" s="3">
-        <v>43.61089324951172</v>
+        <v>43.610893</v>
       </c>
       <c r="AD6" s="3">
         <v>0</v>
@@ -2465,55 +2465,55 @@
         <v>0</v>
       </c>
       <c r="AG6" s="3">
-        <v>0.1271770894527435</v>
+        <v>0.12717709</v>
       </c>
       <c r="AH6" s="3">
-        <v>0.2202585637569427</v>
+        <v>0.22025856</v>
       </c>
       <c r="AI6" s="3">
-        <v>0.8942956924438477</v>
+        <v>0.8942957</v>
       </c>
       <c r="AJ6" s="3">
-        <v>0.06135303899645805</v>
+        <v>0.06135304</v>
       </c>
       <c r="AK6" s="3">
-        <v>0.8039292097091675</v>
+        <v>0.8039292</v>
       </c>
       <c r="AL6" s="3">
-        <v>0.2305876314640045</v>
+        <v>0.23058763</v>
       </c>
       <c r="AM6" s="3">
-        <v>0.6877052187919617</v>
+        <v>0.6877052</v>
       </c>
       <c r="AN6" s="3">
-        <v>0.8726595640182495</v>
+        <v>0.87265956</v>
       </c>
       <c r="AO6" s="3">
-        <v>0.1537323892116547</v>
+        <v>0.15373239</v>
       </c>
       <c r="AP6" s="3">
-        <v>0.9824175834655762</v>
+        <v>0.9824176</v>
       </c>
       <c r="AQ6" s="3">
-        <v>0.9999364018440247</v>
+        <v>0.9999363999999999</v>
       </c>
       <c r="AR6" s="3">
-        <v>0.6918768286705017</v>
+        <v>0.6918768</v>
       </c>
       <c r="AS6" s="3">
-        <v>0.9350003004074097</v>
+        <v>0.9350003</v>
       </c>
       <c r="AT6" s="3">
-        <v>0.8881651163101196</v>
+        <v>0.8881651</v>
       </c>
       <c r="AU6" s="3">
-        <v>-4.572171211242676</v>
+        <v>-4.572171</v>
       </c>
       <c r="AV6" s="3">
-        <v>102.9109344482422</v>
+        <v>102.910934</v>
       </c>
       <c r="AW6" s="3">
-        <v>1.542145013809204</v>
+        <v>1.542145</v>
       </c>
       <c r="AX6" s="3">
         <v>457.5340000000003</v>
@@ -2614,7 +2614,7 @@
         <v>0.5999825960243118</v>
       </c>
       <c r="W7" s="3">
-        <v>3.425800000000002</v>
+        <v>3.425800000000001</v>
       </c>
       <c r="X7" s="3">
         <v>-5.400456887088002</v>
@@ -2628,13 +2628,13 @@
         </is>
       </c>
       <c r="AA7" s="3">
-        <v>65.05916595458984</v>
+        <v>65.059166</v>
       </c>
       <c r="AB7" s="3">
-        <v>60.00357818603516</v>
+        <v>60.00358</v>
       </c>
       <c r="AC7" s="3">
-        <v>44.6668815612793</v>
+        <v>44.66688</v>
       </c>
       <c r="AD7" s="3">
         <v>0</v>
@@ -2646,61 +2646,61 @@
         <v>0</v>
       </c>
       <c r="AG7" s="3">
-        <v>0.1288575828075409</v>
+        <v>0.12885758</v>
       </c>
       <c r="AH7" s="3">
-        <v>0.3298957347869873</v>
+        <v>0.32989573</v>
       </c>
       <c r="AI7" s="3">
-        <v>0.8526568412780762</v>
+        <v>0.85265684</v>
       </c>
       <c r="AJ7" s="3">
-        <v>0.05069895833730698</v>
+        <v>0.05069896</v>
       </c>
       <c r="AK7" s="3">
-        <v>0.9088436365127563</v>
+        <v>0.90884364</v>
       </c>
       <c r="AL7" s="3">
-        <v>0.4120451509952545</v>
+        <v>0.41204515</v>
       </c>
       <c r="AM7" s="3">
-        <v>0.7709028124809265</v>
+        <v>0.7709028</v>
       </c>
       <c r="AN7" s="3">
-        <v>0.8821433782577515</v>
+        <v>0.8821434</v>
       </c>
       <c r="AO7" s="3">
-        <v>0.25823575258255</v>
+        <v>0.25823575</v>
       </c>
       <c r="AP7" s="3">
-        <v>0.9915574193000793</v>
+        <v>0.9915574</v>
       </c>
       <c r="AQ7" s="3">
-        <v>0.999984085559845</v>
+        <v>0.9999841</v>
       </c>
       <c r="AR7" s="3">
-        <v>0.720245361328125</v>
+        <v>0.7202453599999999</v>
       </c>
       <c r="AS7" s="3">
-        <v>0.9579125642776489</v>
+        <v>0.95791256</v>
       </c>
       <c r="AT7" s="3">
-        <v>0.8994634747505188</v>
+        <v>0.8994635</v>
       </c>
       <c r="AU7" s="3">
-        <v>-4.629571437835693</v>
+        <v>-4.6295714</v>
       </c>
       <c r="AV7" s="3">
-        <v>100.5195770263672</v>
+        <v>100.51958</v>
       </c>
       <c r="AW7" s="3">
-        <v>5.763133525848389</v>
+        <v>5.7631335</v>
       </c>
       <c r="AX7" s="3">
         <v>450.5140000000002</v>
       </c>
       <c r="AY7" s="3">
-        <v>3.425800000000002</v>
+        <v>3.425800000000001</v>
       </c>
       <c r="AZ7" s="3">
         <v>0.4368048816560142</v>
@@ -2762,7 +2762,7 @@
         <v>5.442375258869468</v>
       </c>
       <c r="L8" s="3">
-        <v>0.9042563426665993</v>
+        <v>0.9042563426665992</v>
       </c>
       <c r="M8" s="3">
         <v>0.2814547288330222</v>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="AA8" s="3">
-        <v>62.37113189697266</v>
+        <v>62.37113</v>
       </c>
       <c r="AB8" s="3">
-        <v>55.22406768798828</v>
+        <v>55.224068</v>
       </c>
       <c r="AC8" s="3">
-        <v>42.23020553588867</v>
+        <v>42.230206</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -2827,55 +2827,55 @@
         <v>1</v>
       </c>
       <c r="AG8" s="3">
-        <v>0.3101035356521606</v>
+        <v>0.31010354</v>
       </c>
       <c r="AH8" s="3">
-        <v>0.3923474550247192</v>
+        <v>0.39234746</v>
       </c>
       <c r="AI8" s="3">
-        <v>0.8259280920028687</v>
+        <v>0.8259281000000001</v>
       </c>
       <c r="AJ8" s="3">
-        <v>0.06683068722486496</v>
+        <v>0.06683069</v>
       </c>
       <c r="AK8" s="3">
-        <v>0.89606773853302</v>
+        <v>0.89606774</v>
       </c>
       <c r="AL8" s="3">
-        <v>0.3563960790634155</v>
+        <v>0.35639608</v>
       </c>
       <c r="AM8" s="3">
-        <v>0.6407724618911743</v>
+        <v>0.64077246</v>
       </c>
       <c r="AN8" s="3">
-        <v>0.7509437203407288</v>
+        <v>0.7509437</v>
       </c>
       <c r="AO8" s="3">
-        <v>0.2986282110214233</v>
+        <v>0.2986282</v>
       </c>
       <c r="AP8" s="3">
-        <v>0.9887466430664062</v>
+        <v>0.98874664</v>
       </c>
       <c r="AQ8" s="3">
-        <v>0.999965488910675</v>
+        <v>0.9999655</v>
       </c>
       <c r="AR8" s="3">
-        <v>0.7102676630020142</v>
+        <v>0.71026766</v>
       </c>
       <c r="AS8" s="3">
-        <v>0.9408232569694519</v>
+        <v>0.9408232600000001</v>
       </c>
       <c r="AT8" s="3">
-        <v>0.8539096117019653</v>
+        <v>0.8539096</v>
       </c>
       <c r="AU8" s="3">
-        <v>-4.659994602203369</v>
+        <v>-4.6599946</v>
       </c>
       <c r="AV8" s="3">
-        <v>99.01403045654297</v>
+        <v>99.01403000000001</v>
       </c>
       <c r="AW8" s="3">
-        <v>5.339962959289551</v>
+        <v>5.339963</v>
       </c>
       <c r="AX8" s="3">
         <v>441.8900000000002</v>
@@ -2946,7 +2946,7 @@
         <v>0.906621558983175</v>
       </c>
       <c r="M9" s="3">
-        <v>0.2852271842951613</v>
+        <v>0.2852271842951612</v>
       </c>
       <c r="N9" s="3">
         <v>10.07053328495923</v>
@@ -2958,13 +2958,13 @@
         <v>5.093378441016825</v>
       </c>
       <c r="Q9" s="3">
-        <v>0.2852271842951613</v>
+        <v>0.2852271842951612</v>
       </c>
       <c r="R9" s="3">
         <v>2.226262022311256</v>
       </c>
       <c r="S9" s="3">
-        <v>29.21910036574298</v>
+        <v>29.21910036574297</v>
       </c>
       <c r="T9" s="3">
         <v>4.534333159798309</v>
@@ -2973,7 +2973,7 @@
         <v>5.652423722235341</v>
       </c>
       <c r="V9" s="3">
-        <v>0.2852271842951613</v>
+        <v>0.2852271842951612</v>
       </c>
       <c r="W9" s="3">
         <v>3.282300000000002</v>
@@ -2990,13 +2990,13 @@
         </is>
       </c>
       <c r="AA9" s="3">
-        <v>59.43584060668945</v>
+        <v>59.43584</v>
       </c>
       <c r="AB9" s="3">
-        <v>52.18408203125</v>
+        <v>52.184082</v>
       </c>
       <c r="AC9" s="3">
-        <v>41.87752151489258</v>
+        <v>41.87752</v>
       </c>
       <c r="AD9" s="3">
         <v>0</v>
@@ -3008,55 +3008,55 @@
         <v>1</v>
       </c>
       <c r="AG9" s="3">
-        <v>0.2669618129730225</v>
+        <v>0.2669618</v>
       </c>
       <c r="AH9" s="3">
-        <v>0.3822127282619476</v>
+        <v>0.38221273</v>
       </c>
       <c r="AI9" s="3">
-        <v>0.8209371566772461</v>
+        <v>0.8209371600000001</v>
       </c>
       <c r="AJ9" s="3">
-        <v>0.06480167061090469</v>
+        <v>0.06480167000000001</v>
       </c>
       <c r="AK9" s="3">
-        <v>0.8890542984008789</v>
+        <v>0.8890543</v>
       </c>
       <c r="AL9" s="3">
-        <v>0.3441812992095947</v>
+        <v>0.3441813</v>
       </c>
       <c r="AM9" s="3">
-        <v>0.6596811413764954</v>
+        <v>0.65968114</v>
       </c>
       <c r="AN9" s="3">
-        <v>0.7550131678581238</v>
+        <v>0.75501317</v>
       </c>
       <c r="AO9" s="3">
-        <v>0.3046085238456726</v>
+        <v>0.30460852</v>
       </c>
       <c r="AP9" s="3">
-        <v>0.9877355694770813</v>
+        <v>0.98773557</v>
       </c>
       <c r="AQ9" s="3">
-        <v>0.999967098236084</v>
+        <v>0.9999671</v>
       </c>
       <c r="AR9" s="3">
-        <v>0.7097679376602173</v>
+        <v>0.70976794</v>
       </c>
       <c r="AS9" s="3">
-        <v>0.9410902261734009</v>
+        <v>0.9410902</v>
       </c>
       <c r="AT9" s="3">
-        <v>0.8390313982963562</v>
+        <v>0.8390314</v>
       </c>
       <c r="AU9" s="3">
-        <v>-4.638782501220703</v>
+        <v>-4.6387825</v>
       </c>
       <c r="AV9" s="3">
-        <v>98.33652496337891</v>
+        <v>98.33652499999999</v>
       </c>
       <c r="AW9" s="3">
-        <v>5.691188812255859</v>
+        <v>5.691189</v>
       </c>
       <c r="AX9" s="3">
         <v>441.8900000000002</v>
@@ -3127,7 +3127,7 @@
         <v>1.09932861748551</v>
       </c>
       <c r="M10" s="3">
-        <v>0.3108476256889631</v>
+        <v>0.310847625688963</v>
       </c>
       <c r="N10" s="3">
         <v>15.66832694758522</v>
@@ -3139,7 +3139,7 @@
         <v>4.90067138251449</v>
       </c>
       <c r="Q10" s="3">
-        <v>0.3108476256889631</v>
+        <v>0.310847625688963</v>
       </c>
       <c r="R10" s="3">
         <v>3.090774148665433</v>
@@ -3154,7 +3154,7 @@
         <v>5.509932728864858</v>
       </c>
       <c r="V10" s="3">
-        <v>0.3108476256889631</v>
+        <v>0.310847625688963</v>
       </c>
       <c r="W10" s="3">
         <v>3.356100000000002</v>
@@ -3171,13 +3171,13 @@
         </is>
       </c>
       <c r="AA10" s="3">
-        <v>63.35163116455078</v>
+        <v>63.35163</v>
       </c>
       <c r="AB10" s="3">
-        <v>56.5468635559082</v>
+        <v>56.546864</v>
       </c>
       <c r="AC10" s="3">
-        <v>48.16203308105469</v>
+        <v>48.162033</v>
       </c>
       <c r="AD10" s="3">
         <v>1</v>
@@ -3189,55 +3189,55 @@
         <v>0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.1838238537311554</v>
+        <v>0.18382385</v>
       </c>
       <c r="AH10" s="3">
-        <v>0.4433763027191162</v>
+        <v>0.4433763</v>
       </c>
       <c r="AI10" s="3">
-        <v>0.8228710293769836</v>
+        <v>0.822871</v>
       </c>
       <c r="AJ10" s="3">
-        <v>0.04280499368906021</v>
+        <v>0.042804994</v>
       </c>
       <c r="AK10" s="3">
-        <v>0.9336031079292297</v>
+        <v>0.9336031</v>
       </c>
       <c r="AL10" s="3">
-        <v>0.3841913342475891</v>
+        <v>0.38419133</v>
       </c>
       <c r="AM10" s="3">
-        <v>0.6688296794891357</v>
+        <v>0.6688297</v>
       </c>
       <c r="AN10" s="3">
-        <v>0.7798103094100952</v>
+        <v>0.7798103</v>
       </c>
       <c r="AO10" s="3">
-        <v>0.2854128181934357</v>
+        <v>0.28541282</v>
       </c>
       <c r="AP10" s="3">
-        <v>0.9915239214897156</v>
+        <v>0.9915239</v>
       </c>
       <c r="AQ10" s="3">
-        <v>0.9999836683273315</v>
+        <v>0.99998367</v>
       </c>
       <c r="AR10" s="3">
-        <v>0.7591281533241272</v>
+        <v>0.75912815</v>
       </c>
       <c r="AS10" s="3">
-        <v>0.9587962031364441</v>
+        <v>0.9587962</v>
       </c>
       <c r="AT10" s="3">
-        <v>0.8767231106758118</v>
+        <v>0.8767231</v>
       </c>
       <c r="AU10" s="3">
-        <v>-4.84730863571167</v>
+        <v>-4.8473086</v>
       </c>
       <c r="AV10" s="3">
-        <v>100.1038665771484</v>
+        <v>100.10387</v>
       </c>
       <c r="AW10" s="3">
-        <v>8.695140838623047</v>
+        <v>8.695141</v>
       </c>
       <c r="AX10" s="3">
         <v>432.5240000000002</v>
@@ -3323,7 +3323,7 @@
         <v>0.5761692979434486</v>
       </c>
       <c r="R11" s="3">
-        <v>1.285738747074785</v>
+        <v>1.285738747074784</v>
       </c>
       <c r="S11" s="3">
         <v>233.2042065343045</v>
@@ -3352,13 +3352,13 @@
         </is>
       </c>
       <c r="AA11" s="3">
-        <v>50.03407669067383</v>
+        <v>50.034077</v>
       </c>
       <c r="AB11" s="3">
-        <v>47.67665863037109</v>
+        <v>47.67666</v>
       </c>
       <c r="AC11" s="3">
-        <v>41.62461090087891</v>
+        <v>41.62461</v>
       </c>
       <c r="AD11" s="3">
         <v>0</v>
@@ -3370,55 +3370,55 @@
         <v>0</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.2527405619621277</v>
+        <v>0.25274056</v>
       </c>
       <c r="AH11" s="3">
-        <v>0.4688826203346252</v>
+        <v>0.46888262</v>
       </c>
       <c r="AI11" s="3">
-        <v>0.8351690173149109</v>
+        <v>0.8351690000000001</v>
       </c>
       <c r="AJ11" s="3">
-        <v>0.04883063584566116</v>
+        <v>0.048830636</v>
       </c>
       <c r="AK11" s="3">
-        <v>0.9386070370674133</v>
+        <v>0.9386070399999999</v>
       </c>
       <c r="AL11" s="3">
-        <v>0.3703396916389465</v>
+        <v>0.3703397</v>
       </c>
       <c r="AM11" s="3">
-        <v>0.6521977186203003</v>
+        <v>0.6521977</v>
       </c>
       <c r="AN11" s="3">
-        <v>0.7791668176651001</v>
+        <v>0.7791668</v>
       </c>
       <c r="AO11" s="3">
-        <v>0.2660719156265259</v>
+        <v>0.26607192</v>
       </c>
       <c r="AP11" s="3">
-        <v>0.9907934069633484</v>
+        <v>0.9907934</v>
       </c>
       <c r="AQ11" s="3">
-        <v>0.9999765157699585</v>
+        <v>0.9999765</v>
       </c>
       <c r="AR11" s="3">
-        <v>0.7638531923294067</v>
+        <v>0.7638532</v>
       </c>
       <c r="AS11" s="3">
-        <v>0.9541949033737183</v>
+        <v>0.9541949</v>
       </c>
       <c r="AT11" s="3">
-        <v>0.8792737722396851</v>
+        <v>0.8792738</v>
       </c>
       <c r="AU11" s="3">
-        <v>-4.85697603225708</v>
+        <v>-4.856976</v>
       </c>
       <c r="AV11" s="3">
-        <v>99.01522064208984</v>
+        <v>99.01522</v>
       </c>
       <c r="AW11" s="3">
-        <v>8.199435234069824</v>
+        <v>8.199434999999999</v>
       </c>
       <c r="AX11" s="3">
         <v>432.5240000000002</v>
@@ -3513,7 +3513,7 @@
         <v>3.61342715238505</v>
       </c>
       <c r="U12" s="3">
-        <v>5.913916754866499</v>
+        <v>5.9139167548665</v>
       </c>
       <c r="V12" s="3">
         <v>0.5868595924697575</v>
@@ -3533,13 +3533,13 @@
         </is>
       </c>
       <c r="AA12" s="3">
-        <v>57.03730392456055</v>
+        <v>57.037304</v>
       </c>
       <c r="AB12" s="3">
-        <v>52.2125358581543</v>
+        <v>52.212536</v>
       </c>
       <c r="AC12" s="3">
-        <v>41.39736175537109</v>
+        <v>41.39736</v>
       </c>
       <c r="AD12" s="3">
         <v>0</v>
@@ -3551,55 +3551,55 @@
         <v>0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.136568158864975</v>
+        <v>0.13656816</v>
       </c>
       <c r="AH12" s="3">
-        <v>0.3449681401252747</v>
+        <v>0.34496814</v>
       </c>
       <c r="AI12" s="3">
-        <v>0.8326091766357422</v>
+        <v>0.8326092</v>
       </c>
       <c r="AJ12" s="3">
-        <v>0.04591820389032364</v>
+        <v>0.045918204</v>
       </c>
       <c r="AK12" s="3">
-        <v>0.9081462621688843</v>
+        <v>0.90814626</v>
       </c>
       <c r="AL12" s="3">
-        <v>0.3976964354515076</v>
+        <v>0.39769644</v>
       </c>
       <c r="AM12" s="3">
-        <v>0.7110432386398315</v>
+        <v>0.71104324</v>
       </c>
       <c r="AN12" s="3">
-        <v>0.8270397186279297</v>
+        <v>0.8270397</v>
       </c>
       <c r="AO12" s="3">
-        <v>0.2387844771146774</v>
+        <v>0.23878448</v>
       </c>
       <c r="AP12" s="3">
-        <v>0.990247368812561</v>
+        <v>0.99024737</v>
       </c>
       <c r="AQ12" s="3">
-        <v>0.9999844431877136</v>
+        <v>0.99998444</v>
       </c>
       <c r="AR12" s="3">
-        <v>0.7519134283065796</v>
+        <v>0.7519134</v>
       </c>
       <c r="AS12" s="3">
-        <v>0.9603689312934875</v>
+        <v>0.96036893</v>
       </c>
       <c r="AT12" s="3">
-        <v>0.8537232279777527</v>
+        <v>0.8537232</v>
       </c>
       <c r="AU12" s="3">
-        <v>-4.693785667419434</v>
+        <v>-4.6937857</v>
       </c>
       <c r="AV12" s="3">
-        <v>100.2177886962891</v>
+        <v>100.21779</v>
       </c>
       <c r="AW12" s="3">
-        <v>4.988943576812744</v>
+        <v>4.9889436</v>
       </c>
       <c r="AX12" s="3">
         <v>432.5240000000002</v>
@@ -3714,13 +3714,13 @@
         </is>
       </c>
       <c r="AA13" s="3">
-        <v>50.9268913269043</v>
+        <v>50.92689</v>
       </c>
       <c r="AB13" s="3">
-        <v>50.9757194519043</v>
+        <v>50.97572</v>
       </c>
       <c r="AC13" s="3">
-        <v>40.63362884521484</v>
+        <v>40.63363</v>
       </c>
       <c r="AD13" s="3">
         <v>0</v>
@@ -3732,55 +3732,55 @@
         <v>0</v>
       </c>
       <c r="AG13" s="3">
-        <v>0.2754431068897247</v>
+        <v>0.2754431</v>
       </c>
       <c r="AH13" s="3">
-        <v>0.2086796313524246</v>
+        <v>0.20867963</v>
       </c>
       <c r="AI13" s="3">
-        <v>0.9090962409973145</v>
+        <v>0.90909624</v>
       </c>
       <c r="AJ13" s="3">
-        <v>0.06169123575091362</v>
+        <v>0.061691236</v>
       </c>
       <c r="AK13" s="3">
-        <v>0.7485303282737732</v>
+        <v>0.7485303</v>
       </c>
       <c r="AL13" s="3">
-        <v>0.2723855376243591</v>
+        <v>0.27238554</v>
       </c>
       <c r="AM13" s="3">
-        <v>0.656551718711853</v>
+        <v>0.6565517</v>
       </c>
       <c r="AN13" s="3">
-        <v>0.7990891337394714</v>
+        <v>0.79908913</v>
       </c>
       <c r="AO13" s="3">
-        <v>0.108659490942955</v>
+        <v>0.10865949</v>
       </c>
       <c r="AP13" s="3">
-        <v>0.9628103375434875</v>
+        <v>0.96281034</v>
       </c>
       <c r="AQ13" s="3">
-        <v>0.9999311566352844</v>
+        <v>0.99993116</v>
       </c>
       <c r="AR13" s="3">
-        <v>0.7291480302810669</v>
+        <v>0.7291480299999999</v>
       </c>
       <c r="AS13" s="3">
-        <v>0.9398983716964722</v>
+        <v>0.9398984</v>
       </c>
       <c r="AT13" s="3">
-        <v>0.8420951962471008</v>
+        <v>0.8420952</v>
       </c>
       <c r="AU13" s="3">
-        <v>-4.587052822113037</v>
+        <v>-4.587053</v>
       </c>
       <c r="AV13" s="3">
-        <v>98.45797729492188</v>
+        <v>98.45798000000001</v>
       </c>
       <c r="AW13" s="3">
-        <v>5.001123428344727</v>
+        <v>5.0011234</v>
       </c>
       <c r="AX13" s="3">
         <v>442.5190000000002</v>
@@ -3860,7 +3860,7 @@
         <v>76.0808612751983</v>
       </c>
       <c r="P14" s="3">
-        <v>4.797356000773195</v>
+        <v>4.797356000773196</v>
       </c>
       <c r="Q14" s="3">
         <v>0.6027867767415637</v>
@@ -3872,7 +3872,7 @@
         <v>242.1620484371657</v>
       </c>
       <c r="T14" s="3">
-        <v>3.61589391835973</v>
+        <v>3.615893918359729</v>
       </c>
       <c r="U14" s="3">
         <v>5.97881808318666</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="AA14" s="3">
-        <v>59.47090530395508</v>
+        <v>59.470905</v>
       </c>
       <c r="AB14" s="3">
-        <v>57.21721267700195</v>
+        <v>57.217213</v>
       </c>
       <c r="AC14" s="3">
-        <v>40.80252838134766</v>
+        <v>40.80253</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -3913,55 +3913,55 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
-        <v>0.1844686567783356</v>
+        <v>0.18446866</v>
       </c>
       <c r="AH14" s="3">
-        <v>0.420243501663208</v>
+        <v>0.4202435</v>
       </c>
       <c r="AI14" s="3">
-        <v>0.8358315229415894</v>
+        <v>0.8358314999999999</v>
       </c>
       <c r="AJ14" s="3">
-        <v>0.04515017569065094</v>
+        <v>0.045150176</v>
       </c>
       <c r="AK14" s="3">
-        <v>0.9386307597160339</v>
+        <v>0.93863076</v>
       </c>
       <c r="AL14" s="3">
-        <v>0.4181107878684998</v>
+        <v>0.4181108</v>
       </c>
       <c r="AM14" s="3">
-        <v>0.7442826628684998</v>
+        <v>0.74428266</v>
       </c>
       <c r="AN14" s="3">
-        <v>0.8617993593215942</v>
+        <v>0.86179936</v>
       </c>
       <c r="AO14" s="3">
-        <v>0.2975649237632751</v>
+        <v>0.29756492</v>
       </c>
       <c r="AP14" s="3">
-        <v>0.9936869740486145</v>
+        <v>0.993687</v>
       </c>
       <c r="AQ14" s="3">
-        <v>0.9999872446060181</v>
+        <v>0.9999872400000001</v>
       </c>
       <c r="AR14" s="3">
-        <v>0.7217900156974792</v>
+        <v>0.72179</v>
       </c>
       <c r="AS14" s="3">
-        <v>0.9570225477218628</v>
+        <v>0.95702255</v>
       </c>
       <c r="AT14" s="3">
-        <v>0.9055355191230774</v>
+        <v>0.9055355</v>
       </c>
       <c r="AU14" s="3">
-        <v>-4.767285823822021</v>
+        <v>-4.767286</v>
       </c>
       <c r="AV14" s="3">
-        <v>101.1879043579102</v>
+        <v>101.187904</v>
       </c>
       <c r="AW14" s="3">
-        <v>5.74851131439209</v>
+        <v>5.7485113</v>
       </c>
       <c r="AX14" s="3">
         <v>432.5240000000002</v>
@@ -4032,7 +4032,7 @@
         <v>1.131224991912706</v>
       </c>
       <c r="M15" s="3">
-        <v>0.2826193926469747</v>
+        <v>0.2826193926469746</v>
       </c>
       <c r="N15" s="3">
         <v>15.99087106225332</v>
@@ -4044,7 +4044,7 @@
         <v>4.868775008087295</v>
       </c>
       <c r="Q15" s="3">
-        <v>0.2826193926469747</v>
+        <v>0.2826193926469746</v>
       </c>
       <c r="R15" s="3">
         <v>3.778252534271487</v>
@@ -4059,7 +4059,7 @@
         <v>5.422709017675365</v>
       </c>
       <c r="V15" s="3">
-        <v>0.2826193926469747</v>
+        <v>0.2826193926469746</v>
       </c>
       <c r="W15" s="3">
         <v>3.235700000000002</v>
@@ -4076,13 +4076,13 @@
         </is>
       </c>
       <c r="AA15" s="3">
-        <v>39.40145492553711</v>
+        <v>39.401455</v>
       </c>
       <c r="AB15" s="3">
-        <v>34.59626388549805</v>
+        <v>34.596264</v>
       </c>
       <c r="AC15" s="3">
-        <v>65.55100250244141</v>
+        <v>65.551</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -4094,55 +4094,55 @@
         <v>0</v>
       </c>
       <c r="AG15" s="3">
-        <v>0.1470246165990829</v>
+        <v>0.14702462</v>
       </c>
       <c r="AH15" s="3">
-        <v>0.4020842611789703</v>
+        <v>0.40208426</v>
       </c>
       <c r="AI15" s="3">
-        <v>0.8129655122756958</v>
+        <v>0.8129655</v>
       </c>
       <c r="AJ15" s="3">
-        <v>0.06055311113595963</v>
+        <v>0.06055311</v>
       </c>
       <c r="AK15" s="3">
-        <v>0.7664860486984253</v>
+        <v>0.76648605</v>
       </c>
       <c r="AL15" s="3">
-        <v>0.04973115772008896</v>
+        <v>0.049731158</v>
       </c>
       <c r="AM15" s="3">
-        <v>0.1665998250246048</v>
+        <v>0.16659983</v>
       </c>
       <c r="AN15" s="3">
-        <v>0.2822297513484955</v>
+        <v>0.28222975</v>
       </c>
       <c r="AO15" s="3">
-        <v>0.05323129892349243</v>
+        <v>0.0532313</v>
       </c>
       <c r="AP15" s="3">
-        <v>0.6726550459861755</v>
+        <v>0.67265505</v>
       </c>
       <c r="AQ15" s="3">
-        <v>0.9988282918930054</v>
+        <v>0.9988283</v>
       </c>
       <c r="AR15" s="3">
-        <v>0.8737862706184387</v>
+        <v>0.8737863</v>
       </c>
       <c r="AS15" s="3">
-        <v>0.8524991273880005</v>
+        <v>0.8524991</v>
       </c>
       <c r="AT15" s="3">
-        <v>0.5546180605888367</v>
+        <v>0.55461806</v>
       </c>
       <c r="AU15" s="3">
-        <v>-4.882927417755127</v>
+        <v>-4.8829274</v>
       </c>
       <c r="AV15" s="3">
-        <v>92.54988861083984</v>
+        <v>92.54989</v>
       </c>
       <c r="AW15" s="3">
-        <v>14.19005012512207</v>
+        <v>14.19005</v>
       </c>
       <c r="AX15" s="3">
         <v>374.4880000000001</v>
@@ -4257,13 +4257,13 @@
         </is>
       </c>
       <c r="AA16" s="3">
-        <v>54.78041458129883</v>
+        <v>54.780415</v>
       </c>
       <c r="AB16" s="3">
-        <v>53.94894409179688</v>
+        <v>53.948944</v>
       </c>
       <c r="AC16" s="3">
-        <v>42.26363372802734</v>
+        <v>42.263634</v>
       </c>
       <c r="AD16" s="3">
         <v>0</v>
@@ -4275,55 +4275,55 @@
         <v>0</v>
       </c>
       <c r="AG16" s="3">
-        <v>0.1846052557229996</v>
+        <v>0.18460526</v>
       </c>
       <c r="AH16" s="3">
-        <v>0.2568766474723816</v>
+        <v>0.25687665</v>
       </c>
       <c r="AI16" s="3">
-        <v>0.8295854330062866</v>
+        <v>0.82958543</v>
       </c>
       <c r="AJ16" s="3">
-        <v>0.04777414351701736</v>
+        <v>0.047774144</v>
       </c>
       <c r="AK16" s="3">
-        <v>0.7852019071578979</v>
+        <v>0.7852019</v>
       </c>
       <c r="AL16" s="3">
-        <v>0.3549326956272125</v>
+        <v>0.3549327</v>
       </c>
       <c r="AM16" s="3">
-        <v>0.5801857709884644</v>
+        <v>0.5801858</v>
       </c>
       <c r="AN16" s="3">
-        <v>0.6986960172653198</v>
+        <v>0.698696</v>
       </c>
       <c r="AO16" s="3">
-        <v>0.1074317917227745</v>
+        <v>0.10743179</v>
       </c>
       <c r="AP16" s="3">
-        <v>0.9525402188301086</v>
+        <v>0.9525401999999999</v>
       </c>
       <c r="AQ16" s="3">
-        <v>0.9999625086784363</v>
+        <v>0.9999625</v>
       </c>
       <c r="AR16" s="3">
-        <v>0.7946434020996094</v>
+        <v>0.7946434</v>
       </c>
       <c r="AS16" s="3">
-        <v>0.9663586616516113</v>
+        <v>0.96635866</v>
       </c>
       <c r="AT16" s="3">
-        <v>0.7364034056663513</v>
+        <v>0.7364034</v>
       </c>
       <c r="AU16" s="3">
-        <v>-4.514651298522949</v>
+        <v>-4.5146513</v>
       </c>
       <c r="AV16" s="3">
-        <v>97.03193664550781</v>
+        <v>97.03194000000001</v>
       </c>
       <c r="AW16" s="3">
-        <v>7.176081657409668</v>
+        <v>7.1760817</v>
       </c>
       <c r="AX16" s="3">
         <v>410.4680000000001</v>
@@ -4338,7 +4338,7 @@
         <v>4</v>
       </c>
       <c r="BB16" s="3">
-        <v>3.545492488272934</v>
+        <v>3.545492488272933</v>
       </c>
       <c r="BC16" s="3">
         <v>0.7171675013030074</v>
@@ -4438,13 +4438,13 @@
         </is>
       </c>
       <c r="AA17" s="3">
-        <v>43.97466278076172</v>
+        <v>43.974663</v>
       </c>
       <c r="AB17" s="3">
-        <v>45.25797653198242</v>
+        <v>45.257977</v>
       </c>
       <c r="AC17" s="3">
-        <v>40.18251419067383</v>
+        <v>40.182514</v>
       </c>
       <c r="AD17" s="3">
         <v>0</v>
@@ -4456,55 +4456,55 @@
         <v>0</v>
       </c>
       <c r="AG17" s="3">
-        <v>0.3547024428844452</v>
+        <v>0.35470244</v>
       </c>
       <c r="AH17" s="3">
-        <v>0.2755811810493469</v>
+        <v>0.27558118</v>
       </c>
       <c r="AI17" s="3">
-        <v>0.8434333801269531</v>
+        <v>0.8434334</v>
       </c>
       <c r="AJ17" s="3">
-        <v>0.05669543892145157</v>
+        <v>0.05669544</v>
       </c>
       <c r="AK17" s="3">
-        <v>0.8141661882400513</v>
+        <v>0.8141662</v>
       </c>
       <c r="AL17" s="3">
-        <v>0.4688974320888519</v>
+        <v>0.46889743</v>
       </c>
       <c r="AM17" s="3">
-        <v>0.7424625158309937</v>
+        <v>0.7424625</v>
       </c>
       <c r="AN17" s="3">
-        <v>0.7493404746055603</v>
+        <v>0.7493405</v>
       </c>
       <c r="AO17" s="3">
-        <v>0.2017192095518112</v>
+        <v>0.20171921</v>
       </c>
       <c r="AP17" s="3">
-        <v>0.9671052098274231</v>
+        <v>0.9671052</v>
       </c>
       <c r="AQ17" s="3">
-        <v>0.9999781847000122</v>
+        <v>0.9999782</v>
       </c>
       <c r="AR17" s="3">
-        <v>0.7519820332527161</v>
+        <v>0.75198203</v>
       </c>
       <c r="AS17" s="3">
-        <v>0.9571763873100281</v>
+        <v>0.9571764</v>
       </c>
       <c r="AT17" s="3">
-        <v>0.7799458503723145</v>
+        <v>0.7799458500000001</v>
       </c>
       <c r="AU17" s="3">
-        <v>-4.562526702880859</v>
+        <v>-4.5625267</v>
       </c>
       <c r="AV17" s="3">
-        <v>96.4825439453125</v>
+        <v>96.482544</v>
       </c>
       <c r="AW17" s="3">
-        <v>6.922297477722168</v>
+        <v>6.9222975</v>
       </c>
       <c r="AX17" s="3">
         <v>421.4720000000002</v>
@@ -4522,7 +4522,7 @@
         <v>5.550955981276114</v>
       </c>
       <c r="BC17" s="3">
-        <v>0.4943382243026541</v>
+        <v>0.494338224302654</v>
       </c>
       <c r="BD17" s="3">
         <v>1</v>
@@ -4619,13 +4619,13 @@
         </is>
       </c>
       <c r="AA18" s="3">
-        <v>56.79734420776367</v>
+        <v>56.797344</v>
       </c>
       <c r="AB18" s="3">
-        <v>54.97663497924805</v>
+        <v>54.976635</v>
       </c>
       <c r="AC18" s="3">
-        <v>41.23449325561523</v>
+        <v>41.234493</v>
       </c>
       <c r="AD18" s="3">
         <v>0</v>
@@ -4637,55 +4637,55 @@
         <v>0</v>
       </c>
       <c r="AG18" s="3">
-        <v>0.1455189734697342</v>
+        <v>0.14551897</v>
       </c>
       <c r="AH18" s="3">
-        <v>0.261256992816925</v>
+        <v>0.261257</v>
       </c>
       <c r="AI18" s="3">
-        <v>0.8253568410873413</v>
+        <v>0.82535684</v>
       </c>
       <c r="AJ18" s="3">
-        <v>0.04628502205014229</v>
+        <v>0.046285022</v>
       </c>
       <c r="AK18" s="3">
-        <v>0.7184890508651733</v>
+        <v>0.71848905</v>
       </c>
       <c r="AL18" s="3">
-        <v>0.1372951120138168</v>
+        <v>0.13729511</v>
       </c>
       <c r="AM18" s="3">
-        <v>0.274469405412674</v>
+        <v>0.2744694</v>
       </c>
       <c r="AN18" s="3">
-        <v>0.3504953980445862</v>
+        <v>0.3504954</v>
       </c>
       <c r="AO18" s="3">
-        <v>0.03136883676052094</v>
+        <v>0.031368837</v>
       </c>
       <c r="AP18" s="3">
-        <v>0.873134970664978</v>
+        <v>0.873135</v>
       </c>
       <c r="AQ18" s="3">
-        <v>0.9999235868453979</v>
+        <v>0.9999236</v>
       </c>
       <c r="AR18" s="3">
-        <v>0.8855177164077759</v>
+        <v>0.8855177</v>
       </c>
       <c r="AS18" s="3">
-        <v>0.9624919891357422</v>
+        <v>0.962492</v>
       </c>
       <c r="AT18" s="3">
-        <v>0.6404985785484314</v>
+        <v>0.6404986</v>
       </c>
       <c r="AU18" s="3">
-        <v>-4.540433406829834</v>
+        <v>-4.5404334</v>
       </c>
       <c r="AV18" s="3">
-        <v>94.15052032470703</v>
+        <v>94.15052</v>
       </c>
       <c r="AW18" s="3">
-        <v>6.388451099395752</v>
+        <v>6.388451</v>
       </c>
       <c r="AX18" s="3">
         <v>393.4620000000002</v>
@@ -4753,7 +4753,7 @@
         <v>5.373032676973282</v>
       </c>
       <c r="L19" s="3">
-        <v>0.9412992172191981</v>
+        <v>0.941299217219198</v>
       </c>
       <c r="M19" s="3">
         <v>0.3091094834936228</v>
@@ -4800,13 +4800,13 @@
         </is>
       </c>
       <c r="AA19" s="3">
-        <v>44.03082275390625</v>
+        <v>44.030823</v>
       </c>
       <c r="AB19" s="3">
-        <v>52.28588104248047</v>
+        <v>52.28588</v>
       </c>
       <c r="AC19" s="3">
-        <v>46.47860717773438</v>
+        <v>46.478607</v>
       </c>
       <c r="AD19" s="3">
         <v>0</v>
@@ -4818,55 +4818,55 @@
         <v>0</v>
       </c>
       <c r="AG19" s="3">
-        <v>0.1481299102306366</v>
+        <v>0.14812991</v>
       </c>
       <c r="AH19" s="3">
-        <v>0.2408363074064255</v>
+        <v>0.2408363</v>
       </c>
       <c r="AI19" s="3">
-        <v>0.7796632647514343</v>
+        <v>0.77966326</v>
       </c>
       <c r="AJ19" s="3">
-        <v>0.04402392357587814</v>
+        <v>0.044023924</v>
       </c>
       <c r="AK19" s="3">
-        <v>0.6242526769638062</v>
+        <v>0.6242527</v>
       </c>
       <c r="AL19" s="3">
-        <v>0.1550628393888474</v>
+        <v>0.15506284</v>
       </c>
       <c r="AM19" s="3">
-        <v>0.2458717375993729</v>
+        <v>0.24587174</v>
       </c>
       <c r="AN19" s="3">
-        <v>0.2648356854915619</v>
+        <v>0.2648357</v>
       </c>
       <c r="AO19" s="3">
-        <v>0.03013483248651028</v>
+        <v>0.030134832</v>
       </c>
       <c r="AP19" s="3">
-        <v>0.7748693227767944</v>
+        <v>0.7748693</v>
       </c>
       <c r="AQ19" s="3">
-        <v>0.9999569058418274</v>
+        <v>0.9999569</v>
       </c>
       <c r="AR19" s="3">
-        <v>0.8821443319320679</v>
+        <v>0.88214433</v>
       </c>
       <c r="AS19" s="3">
-        <v>0.9609131813049316</v>
+        <v>0.9609132</v>
       </c>
       <c r="AT19" s="3">
-        <v>0.4224107265472412</v>
+        <v>0.42241073</v>
       </c>
       <c r="AU19" s="3">
-        <v>-4.425469875335693</v>
+        <v>-4.42547</v>
       </c>
       <c r="AV19" s="3">
-        <v>90.94108581542969</v>
+        <v>90.941086</v>
       </c>
       <c r="AW19" s="3">
-        <v>7.257086753845215</v>
+        <v>7.2570868</v>
       </c>
       <c r="AX19" s="3">
         <v>367.3990000000001</v>
@@ -4934,7 +4934,7 @@
         <v>5.333110587953482</v>
       </c>
       <c r="L20" s="3">
-        <v>1.285779747115499</v>
+        <v>1.2857797471155</v>
       </c>
       <c r="M20" s="3">
         <v>0.5660440593413817</v>
@@ -4981,13 +4981,13 @@
         </is>
       </c>
       <c r="AA20" s="3">
-        <v>50.13816070556641</v>
+        <v>50.13816</v>
       </c>
       <c r="AB20" s="3">
-        <v>44.29613494873047</v>
+        <v>44.296135</v>
       </c>
       <c r="AC20" s="3">
-        <v>40.07870101928711</v>
+        <v>40.0787</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
@@ -4999,55 +4999,55 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
-        <v>0.1225241646170616</v>
+        <v>0.122524165</v>
       </c>
       <c r="AH20" s="3">
-        <v>0.4076254963874817</v>
+        <v>0.4076255</v>
       </c>
       <c r="AI20" s="3">
-        <v>0.8074982762336731</v>
+        <v>0.8074983</v>
       </c>
       <c r="AJ20" s="3">
-        <v>0.06538529694080353</v>
+        <v>0.06538529999999999</v>
       </c>
       <c r="AK20" s="3">
-        <v>0.9155147671699524</v>
+        <v>0.91551477</v>
       </c>
       <c r="AL20" s="3">
-        <v>0.1662097722291946</v>
+        <v>0.16620977</v>
       </c>
       <c r="AM20" s="3">
-        <v>0.5733925700187683</v>
+        <v>0.57339257</v>
       </c>
       <c r="AN20" s="3">
-        <v>0.7777832746505737</v>
+        <v>0.7777833</v>
       </c>
       <c r="AO20" s="3">
-        <v>0.2546526491641998</v>
+        <v>0.25465265</v>
       </c>
       <c r="AP20" s="3">
-        <v>0.9873093366622925</v>
+        <v>0.98730934</v>
       </c>
       <c r="AQ20" s="3">
-        <v>0.9999286532402039</v>
+        <v>0.99992865</v>
       </c>
       <c r="AR20" s="3">
-        <v>0.7207186818122864</v>
+        <v>0.7207187</v>
       </c>
       <c r="AS20" s="3">
-        <v>0.9336918592453003</v>
+        <v>0.93369186</v>
       </c>
       <c r="AT20" s="3">
-        <v>0.9206260442733765</v>
+        <v>0.92062604</v>
       </c>
       <c r="AU20" s="3">
-        <v>-4.77137279510498</v>
+        <v>-4.771373</v>
       </c>
       <c r="AV20" s="3">
-        <v>96.17954254150391</v>
+        <v>96.17954</v>
       </c>
       <c r="AW20" s="3">
-        <v>9.398275375366211</v>
+        <v>9.398275</v>
       </c>
       <c r="AX20" s="3">
         <v>479.5520000000002</v>
@@ -5124,7 +5124,7 @@
         <v>12.12319990519978</v>
       </c>
       <c r="O21" s="3">
-        <v>11.30303816696889</v>
+        <v>11.3030381669689</v>
       </c>
       <c r="P21" s="3">
         <v>5.04820129151144</v>
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="AA21" s="3">
-        <v>24.07105827331543</v>
+        <v>24.071058</v>
       </c>
       <c r="AB21" s="3">
-        <v>23.20031547546387</v>
+        <v>23.200315</v>
       </c>
       <c r="AC21" s="3">
-        <v>48.26595687866211</v>
+        <v>48.265957</v>
       </c>
       <c r="AD21" s="3">
         <v>0</v>
@@ -5180,55 +5180,55 @@
         <v>0</v>
       </c>
       <c r="AG21" s="3">
-        <v>0.1182065382599831</v>
+        <v>0.11820654</v>
       </c>
       <c r="AH21" s="3">
-        <v>0.6393347382545471</v>
+        <v>0.63933474</v>
       </c>
       <c r="AI21" s="3">
-        <v>0.6041701436042786</v>
+        <v>0.60417014</v>
       </c>
       <c r="AJ21" s="3">
-        <v>0.1051495298743248</v>
+        <v>0.10514953</v>
       </c>
       <c r="AK21" s="3">
-        <v>0.9317499995231628</v>
+        <v>0.93175</v>
       </c>
       <c r="AL21" s="3">
-        <v>0.1908909678459167</v>
+        <v>0.19089097</v>
       </c>
       <c r="AM21" s="3">
-        <v>0.2398413717746735</v>
+        <v>0.23984137</v>
       </c>
       <c r="AN21" s="3">
-        <v>0.3507117331027985</v>
+        <v>0.35071173</v>
       </c>
       <c r="AO21" s="3">
-        <v>0.4600063264369965</v>
+        <v>0.46000633</v>
       </c>
       <c r="AP21" s="3">
-        <v>0.8681474924087524</v>
+        <v>0.8681475</v>
       </c>
       <c r="AQ21" s="3">
-        <v>0.9994595646858215</v>
+        <v>0.99945956</v>
       </c>
       <c r="AR21" s="3">
-        <v>0.7938547134399414</v>
+        <v>0.7938547</v>
       </c>
       <c r="AS21" s="3">
-        <v>0.8756176233291626</v>
+        <v>0.8756176</v>
       </c>
       <c r="AT21" s="3">
-        <v>0.7619529962539673</v>
+        <v>0.761953</v>
       </c>
       <c r="AU21" s="3">
-        <v>-4.984997749328613</v>
+        <v>-4.9849977</v>
       </c>
       <c r="AV21" s="3">
-        <v>94.06256103515625</v>
+        <v>94.06256</v>
       </c>
       <c r="AW21" s="3">
-        <v>10.70411491394043</v>
+        <v>10.704115</v>
       </c>
       <c r="AX21" s="3">
         <v>420.5320000000001</v>
@@ -5296,7 +5296,7 @@
         <v>5.302380392493043</v>
       </c>
       <c r="L22" s="3">
-        <v>1.468949255123885</v>
+        <v>1.468949255123884</v>
       </c>
       <c r="M22" s="3">
         <v>0.5084145020066517</v>
@@ -5343,13 +5343,13 @@
         </is>
       </c>
       <c r="AA22" s="3">
-        <v>26.9423828125</v>
+        <v>26.942383</v>
       </c>
       <c r="AB22" s="3">
-        <v>26.06549453735352</v>
+        <v>26.065495</v>
       </c>
       <c r="AC22" s="3">
-        <v>42.71130752563477</v>
+        <v>42.711308</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -5361,55 +5361,55 @@
         <v>0</v>
       </c>
       <c r="AG22" s="3">
-        <v>0.1288079172372818</v>
+        <v>0.12880792</v>
       </c>
       <c r="AH22" s="3">
-        <v>0.6069123148918152</v>
+        <v>0.6069123</v>
       </c>
       <c r="AI22" s="3">
-        <v>0.6032912135124207</v>
+        <v>0.6032912</v>
       </c>
       <c r="AJ22" s="3">
-        <v>0.1614061444997787</v>
+        <v>0.16140614</v>
       </c>
       <c r="AK22" s="3">
-        <v>0.9180282354354858</v>
+        <v>0.9180282400000001</v>
       </c>
       <c r="AL22" s="3">
-        <v>0.1082175821065903</v>
+        <v>0.10821758</v>
       </c>
       <c r="AM22" s="3">
-        <v>0.2446119785308838</v>
+        <v>0.24461198</v>
       </c>
       <c r="AN22" s="3">
-        <v>0.4166762828826904</v>
+        <v>0.41667628</v>
       </c>
       <c r="AO22" s="3">
-        <v>0.4722577929496765</v>
+        <v>0.4722578</v>
       </c>
       <c r="AP22" s="3">
-        <v>0.8204441070556641</v>
+        <v>0.8204441</v>
       </c>
       <c r="AQ22" s="3">
-        <v>0.9939688444137573</v>
+        <v>0.99396884</v>
       </c>
       <c r="AR22" s="3">
-        <v>0.7056134939193726</v>
+        <v>0.7056135</v>
       </c>
       <c r="AS22" s="3">
-        <v>0.7123126983642578</v>
+        <v>0.7123127</v>
       </c>
       <c r="AT22" s="3">
-        <v>0.7908890843391418</v>
+        <v>0.7908891</v>
       </c>
       <c r="AU22" s="3">
-        <v>-5.288914680480957</v>
+        <v>-5.2889147</v>
       </c>
       <c r="AV22" s="3">
-        <v>93.16795349121094</v>
+        <v>93.16795</v>
       </c>
       <c r="AW22" s="3">
-        <v>12.64872550964355</v>
+        <v>12.6487255</v>
       </c>
       <c r="AX22" s="3">
         <v>446.5950000000002</v>
@@ -5424,7 +5424,7 @@
         <v>4</v>
       </c>
       <c r="BB22" s="3">
-        <v>3.23757359000169</v>
+        <v>3.237573590001689</v>
       </c>
       <c r="BC22" s="3">
         <v>0.7513807122220345</v>
@@ -5524,13 +5524,13 @@
         </is>
       </c>
       <c r="AA23" s="3">
-        <v>27.41789627075195</v>
+        <v>27.417896</v>
       </c>
       <c r="AB23" s="3">
-        <v>27.33228492736816</v>
+        <v>27.332285</v>
       </c>
       <c r="AC23" s="3">
-        <v>42.15214538574219</v>
+        <v>42.152145</v>
       </c>
       <c r="AD23" s="3">
         <v>0</v>
@@ -5542,55 +5542,55 @@
         <v>0</v>
       </c>
       <c r="AG23" s="3">
-        <v>0.1247859373688698</v>
+        <v>0.12478594</v>
       </c>
       <c r="AH23" s="3">
-        <v>0.5981893539428711</v>
+        <v>0.59818935</v>
       </c>
       <c r="AI23" s="3">
-        <v>0.6001623272895813</v>
+        <v>0.6001623</v>
       </c>
       <c r="AJ23" s="3">
-        <v>0.1529196500778198</v>
+        <v>0.15291965</v>
       </c>
       <c r="AK23" s="3">
-        <v>0.9381507635116577</v>
+        <v>0.93815076</v>
       </c>
       <c r="AL23" s="3">
-        <v>0.1460613757371902</v>
+        <v>0.14606138</v>
       </c>
       <c r="AM23" s="3">
-        <v>0.3064966797828674</v>
+        <v>0.30649668</v>
       </c>
       <c r="AN23" s="3">
-        <v>0.4617744982242584</v>
+        <v>0.4617745</v>
       </c>
       <c r="AO23" s="3">
-        <v>0.5303400754928589</v>
+        <v>0.5303401</v>
       </c>
       <c r="AP23" s="3">
-        <v>0.8747202157974243</v>
+        <v>0.8747201999999999</v>
       </c>
       <c r="AQ23" s="3">
-        <v>0.9975452423095703</v>
+        <v>0.99754524</v>
       </c>
       <c r="AR23" s="3">
-        <v>0.7082952260971069</v>
+        <v>0.7082952</v>
       </c>
       <c r="AS23" s="3">
-        <v>0.7794957756996155</v>
+        <v>0.7794958</v>
       </c>
       <c r="AT23" s="3">
-        <v>0.8123594522476196</v>
+        <v>0.81235945</v>
       </c>
       <c r="AU23" s="3">
-        <v>-5.267570972442627</v>
+        <v>-5.267571</v>
       </c>
       <c r="AV23" s="3">
-        <v>93.34309387207031</v>
+        <v>93.34309399999999</v>
       </c>
       <c r="AW23" s="3">
-        <v>12.39145660400391</v>
+        <v>12.391457</v>
       </c>
       <c r="AX23" s="3">
         <v>446.5950000000002</v>
@@ -5705,13 +5705,13 @@
         </is>
       </c>
       <c r="AA24" s="3">
-        <v>26.94991493225098</v>
+        <v>26.949915</v>
       </c>
       <c r="AB24" s="3">
-        <v>27.42374610900879</v>
+        <v>27.423746</v>
       </c>
       <c r="AC24" s="3">
-        <v>44.13147735595703</v>
+        <v>44.131477</v>
       </c>
       <c r="AD24" s="3">
         <v>0</v>
@@ -5723,55 +5723,55 @@
         <v>0</v>
       </c>
       <c r="AG24" s="3">
-        <v>0.1374343633651733</v>
+        <v>0.13743436</v>
       </c>
       <c r="AH24" s="3">
-        <v>0.6197664737701416</v>
+        <v>0.6197665</v>
       </c>
       <c r="AI24" s="3">
-        <v>0.6153205037117004</v>
+        <v>0.6153205</v>
       </c>
       <c r="AJ24" s="3">
-        <v>0.1458405554294586</v>
+        <v>0.14584056</v>
       </c>
       <c r="AK24" s="3">
-        <v>0.9333389401435852</v>
+        <v>0.93333894</v>
       </c>
       <c r="AL24" s="3">
-        <v>0.1024077385663986</v>
+        <v>0.10240774</v>
       </c>
       <c r="AM24" s="3">
-        <v>0.2527661025524139</v>
+        <v>0.2527661</v>
       </c>
       <c r="AN24" s="3">
-        <v>0.4209348559379578</v>
+        <v>0.42093486</v>
       </c>
       <c r="AO24" s="3">
-        <v>0.4612038135528564</v>
+        <v>0.4612038</v>
       </c>
       <c r="AP24" s="3">
-        <v>0.8580198287963867</v>
+        <v>0.8580198</v>
       </c>
       <c r="AQ24" s="3">
-        <v>0.9962286949157715</v>
+        <v>0.9962287</v>
       </c>
       <c r="AR24" s="3">
-        <v>0.6946978569030762</v>
+        <v>0.69469786</v>
       </c>
       <c r="AS24" s="3">
-        <v>0.762566864490509</v>
+        <v>0.76256686</v>
       </c>
       <c r="AT24" s="3">
-        <v>0.8615495562553406</v>
+        <v>0.86154956</v>
       </c>
       <c r="AU24" s="3">
-        <v>-5.275237083435059</v>
+        <v>-5.275237</v>
       </c>
       <c r="AV24" s="3">
-        <v>94.41544342041016</v>
+        <v>94.41544</v>
       </c>
       <c r="AW24" s="3">
-        <v>12.82145977020264</v>
+        <v>12.82146</v>
       </c>
       <c r="AX24" s="3">
         <v>460.6220000000002</v>
@@ -5780,13 +5780,13 @@
         <v>3.447800000000002</v>
       </c>
       <c r="AZ24" s="3">
-        <v>0.4432089065478663</v>
+        <v>0.4432089065478662</v>
       </c>
       <c r="BA24" s="3">
         <v>4</v>
       </c>
       <c r="BB24" s="3">
-        <v>3.248638951411451</v>
+        <v>3.24863895141145</v>
       </c>
       <c r="BC24" s="3">
         <v>0.7501512276209499</v>
@@ -5857,7 +5857,7 @@
         <v>0.5417904351222217</v>
       </c>
       <c r="R25" s="3">
-        <v>1.974734185099057</v>
+        <v>1.974734185099056</v>
       </c>
       <c r="S25" s="3">
         <v>262.6196088127128</v>
@@ -5886,13 +5886,13 @@
         </is>
       </c>
       <c r="AA25" s="3">
-        <v>22.30717849731445</v>
+        <v>22.307178</v>
       </c>
       <c r="AB25" s="3">
-        <v>20.03717041015625</v>
+        <v>20.03717</v>
       </c>
       <c r="AC25" s="3">
-        <v>52.28086471557617</v>
+        <v>52.280865</v>
       </c>
       <c r="AD25" s="3">
         <v>0</v>
@@ -5904,55 +5904,55 @@
         <v>0</v>
       </c>
       <c r="AG25" s="3">
-        <v>0.1634543836116791</v>
+        <v>0.16345438</v>
       </c>
       <c r="AH25" s="3">
-        <v>0.69719398021698</v>
+        <v>0.697194</v>
       </c>
       <c r="AI25" s="3">
-        <v>0.6966174840927124</v>
+        <v>0.6966175</v>
       </c>
       <c r="AJ25" s="3">
-        <v>0.08969704806804657</v>
+        <v>0.08969705</v>
       </c>
       <c r="AK25" s="3">
-        <v>0.9630613327026367</v>
+        <v>0.96306133</v>
       </c>
       <c r="AL25" s="3">
-        <v>0.2257703989744186</v>
+        <v>0.2257704</v>
       </c>
       <c r="AM25" s="3">
-        <v>0.3366061151027679</v>
+        <v>0.33660612</v>
       </c>
       <c r="AN25" s="3">
-        <v>0.5271130800247192</v>
+        <v>0.5271131</v>
       </c>
       <c r="AO25" s="3">
-        <v>0.4627063870429993</v>
+        <v>0.4627064</v>
       </c>
       <c r="AP25" s="3">
-        <v>0.9494125247001648</v>
+        <v>0.9494125</v>
       </c>
       <c r="AQ25" s="3">
-        <v>0.9993936419487</v>
+        <v>0.99939364</v>
       </c>
       <c r="AR25" s="3">
-        <v>0.7522884607315063</v>
+        <v>0.75228846</v>
       </c>
       <c r="AS25" s="3">
-        <v>0.8586668968200684</v>
+        <v>0.8586669</v>
       </c>
       <c r="AT25" s="3">
-        <v>0.8462157249450684</v>
+        <v>0.8462157</v>
       </c>
       <c r="AU25" s="3">
-        <v>-5.302098274230957</v>
+        <v>-5.3020983</v>
       </c>
       <c r="AV25" s="3">
-        <v>92.66982269287109</v>
+        <v>92.66982</v>
       </c>
       <c r="AW25" s="3">
-        <v>12.74984169006348</v>
+        <v>12.749842</v>
       </c>
       <c r="AX25" s="3">
         <v>431.5840000000002</v>
